--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487892_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487892_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.8727</v>
+        <v>10.5236</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8895</v>
+        <v>6.2762</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9832</v>
+        <v>4.2474</v>
       </c>
       <c r="G2" t="n">
         <v>6.7324</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7587</v>
+        <v>-0.1078</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4319</v>
+        <v>-0.0452</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3268</v>
+        <v>-0.0626</v>
       </c>
       <c r="V2" t="n">
         <v>5.1477</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0097</v>
+        <v>4.2493</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0292</v>
+        <v>-0.6137</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9805</v>
+        <v>4.863</v>
       </c>
       <c r="G3" t="n">
         <v>1.88</v>
@@ -688,13 +688,13 @@
         <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6271</v>
+        <v>0.8667</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.0401</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.8267</v>
       </c>
       <c r="V3" t="n">
         <v>2.3351</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9993</v>
+        <v>3.7524</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.194</v>
+        <v>-0.0868</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1933</v>
+        <v>3.8392</v>
       </c>
       <c r="G4" t="n">
         <v>4.4488</v>
@@ -766,13 +766,13 @@
         <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1195</v>
+        <v>-0.3665</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8358</v>
+        <v>-0.7286</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2838</v>
+        <v>0.3621</v>
       </c>
       <c r="V4" t="n">
         <v>1.7513</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7586</v>
+        <v>2.8007</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.8033</v>
+        <v>-0.8324</v>
       </c>
       <c r="F5" t="n">
-        <v>5.5619</v>
+        <v>3.6331</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3834</v>
+        <v>5.1676</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7311</v>
+        <v>2.7061</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6523</v>
+        <v>2.4615</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3221</v>
+        <v>2.9144</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4577</v>
+        <v>1.6694</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1355</v>
+        <v>1.245</v>
       </c>
       <c r="M5" t="n">
-        <v>2.0613</v>
+        <v>2.2532</v>
       </c>
       <c r="N5" t="n">
-        <v>1.2734</v>
+        <v>1.0367</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7879</v>
+        <v>1.2165</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.2893</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q5" t="n">
         <v>-4.1624</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8731</v>
+        <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>1.267</v>
+        <v>-0.0557</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5905</v>
+        <v>-0.7519</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8575</v>
+        <v>0.6962</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3975</v>
+        <v>-0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6275</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5864</v>
+        <v>2.3301</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0467</v>
+        <v>0.0029</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6331</v>
+        <v>2.3272</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1676</v>
+        <v>-1.1486</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7061</v>
+        <v>0.405</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4615</v>
+        <v>-1.5537</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9144</v>
+        <v>-1.9037</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6694</v>
+        <v>0.0827</v>
       </c>
       <c r="L6" t="n">
-        <v>1.245</v>
+        <v>-1.9864</v>
       </c>
       <c r="M6" t="n">
-        <v>2.2532</v>
+        <v>0.755</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0367</v>
+        <v>0.3223</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2165</v>
+        <v>0.4327</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2701</v>
+        <v>0.0219</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9663</v>
+        <v>-0.0747</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6962</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1675</v>
+        <v>1.9813</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3975</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.168</v>
+        <v>2.169</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2767</v>
+        <v>2.6358</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4447</v>
+        <v>-0.4668</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1486</v>
+        <v>0.2735</v>
       </c>
       <c r="H7" t="n">
-        <v>0.405</v>
+        <v>1.8019</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5537</v>
+        <v>-1.5283</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9037</v>
+        <v>0.3226</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0827</v>
+        <v>0.9978</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9864</v>
+        <v>-0.6752</v>
       </c>
       <c r="M7" t="n">
-        <v>0.755</v>
+        <v>-0.0491</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3223</v>
+        <v>0.8041</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4327</v>
+        <v>-0.8532</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1402</v>
+        <v>0.063</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3543</v>
+        <v>-0.0219</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2141</v>
+        <v>0.0849</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1675</v>
+        <v>0.5838</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9813</v>
+        <v>2.3351</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8137</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0362</v>
+        <v>1.7978</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3562</v>
+        <v>-3.0595</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.32</v>
+        <v>4.8573</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2735</v>
+        <v>2.3834</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8019</v>
+        <v>1.7311</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5283</v>
+        <v>0.6523</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3226</v>
+        <v>0.3221</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9978</v>
+        <v>0.4577</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6752</v>
+        <v>-0.1355</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0491</v>
+        <v>2.0613</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8041</v>
+        <v>1.2734</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8532</v>
+        <v>0.7879</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0698</v>
+        <v>0.3062</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3014</v>
+        <v>-0.8467</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2317</v>
+        <v>1.1529</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3351</v>
+        <v>1.6275</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7513</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.101</v>
+        <v>0.8639</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1124</v>
+        <v>-0.0367</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9887</v>
+        <v>0.9006</v>
       </c>
       <c r="G9" t="n">
         <v>0.1997</v>
@@ -1156,13 +1156,13 @@
         <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4632</v>
+        <v>0.2261</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4129</v>
+        <v>0.2639</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0503</v>
+        <v>-0.0378</v>
       </c>
       <c r="V9" t="n">
         <v>0.23</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1529</v>
+        <v>0.4655</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5682</v>
+        <v>-2.461</v>
       </c>
       <c r="F10" t="n">
-        <v>2.721</v>
+        <v>2.9266</v>
       </c>
       <c r="G10" t="n">
         <v>0.469</v>
@@ -1234,13 +1234,13 @@
         <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6054</v>
+        <v>-0.2928</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9663</v>
+        <v>-0.8591</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3608</v>
+        <v>0.5663</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4533</v>
+        <v>-1.3945</v>
       </c>
       <c r="E11" t="n">
         <v>-0.0921</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3612</v>
+        <v>-1.3024</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1168</v>
@@ -1312,13 +1312,13 @@
         <v>0.2081</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3771</v>
+        <v>-0.3184</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1675</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>27.2315</v>
+        <v>27.5578</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4063</v>
+        <v>1.7327</v>
       </c>
       <c r="F12" t="n">
         <v>25.8252</v>
@@ -1369,7 +1369,7 @@
         <v>8.227699999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0408</v>
+        <v>1.040800000000001</v>
       </c>
       <c r="M12" t="n">
         <v>11.0205</v>
@@ -1390,13 +1390,13 @@
         <v>16.6495</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01649999999999974</v>
+        <v>0.3427</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.4811</v>
+        <v>-3.1546</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4975</v>
+        <v>3.4974</v>
       </c>
       <c r="V12" t="n">
         <v>10.0479</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0856</v>
+        <v>1.0333</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9731</v>
+        <v>1.7232</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8875</v>
+        <v>-0.6898</v>
       </c>
       <c r="G13" t="n">
         <v>1.7964</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.124</v>
+        <v>0.8238</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2891</v>
+        <v>0.461</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1651</v>
+        <v>0.3628</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2112</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3792</v>
+        <v>-0.0117</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.4334</v>
+        <v>-2.3262</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0542</v>
+        <v>2.3145</v>
       </c>
       <c r="G14" t="n">
         <v>-4.657</v>
@@ -1546,13 +1546,13 @@
         <v>2.7055</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1402</v>
+        <v>0.5077</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4881</v>
+        <v>-0.3809</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6283</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>3.5132</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5688</v>
+        <v>-0.5101</v>
       </c>
       <c r="E15" t="n">
         <v>-0.3262</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2426</v>
+        <v>-0.1839</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4899</v>
@@ -1624,13 +1624,13 @@
         <v>0.2081</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2871</v>
+        <v>-0.2284</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6585</v>
+        <v>-1.4473</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5524</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8939</v>
+        <v>-0.475</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2191</v>
+        <v>-0.7763</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.486</v>
+        <v>-0.7395</v>
       </c>
       <c r="I16" t="n">
-        <v>0.267</v>
+        <v>-0.0367</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0675</v>
+        <v>-0.0494</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4901</v>
+        <v>0.1343</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5576</v>
+        <v>-0.1837</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1515</v>
+        <v>-0.7269</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9761</v>
+        <v>-0.8738</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8246</v>
+        <v>0.147</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1218</v>
+        <v>2.2893</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4053</v>
+        <v>-0.275</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7367</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>2.142</v>
+        <v>0.6479</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.9259</v>
+        <v>-2.6853</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.2183</v>
+        <v>-2.6853</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0726</v>
+        <v>-1.6259</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.758</v>
+        <v>-2.8739</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3147</v>
+        <v>1.248</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7763</v>
+        <v>-1.2191</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7395</v>
+        <v>-1.486</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0367</v>
+        <v>0.267</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0494</v>
+        <v>-0.0675</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1343</v>
+        <v>0.4901</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1837</v>
+        <v>-0.5576</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7269</v>
+        <v>-1.1515</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8738</v>
+        <v>-1.9761</v>
       </c>
       <c r="O17" t="n">
-        <v>0.147</v>
+        <v>0.8246</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2893</v>
+        <v>2.0812</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2893</v>
+        <v>3.1218</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9004</v>
+        <v>0.4379</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7086</v>
+        <v>-1.0581</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1918</v>
+        <v>1.4961</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.6853</v>
+        <v>-2.9259</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6853</v>
+        <v>-2.2183</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1748</v>
+        <v>-2.4925</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.11</v>
+        <v>-2.4857</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0648</v>
+        <v>-0.0067</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8501</v>
+        <v>0.509</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1045</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.9546</v>
+        <v>1.3512</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8581</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2067</v>
+        <v>-0.4501</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0647</v>
+        <v>0.9919</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9921</v>
+        <v>-0.0328</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1022</v>
+        <v>-0.3921</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8899</v>
+        <v>0.3592</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4568</v>
+        <v>2.2893</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5434</v>
+        <v>-0.1842</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7887</v>
+        <v>-0.4895</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2453</v>
+        <v>0.3054</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2843</v>
+        <v>-1.9848</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2843</v>
+        <v>-2.5686</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3052</v>
+        <v>-3.6391</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8072</v>
+        <v>-2.8601</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.498</v>
+        <v>-0.779</v>
       </c>
       <c r="G19" t="n">
-        <v>0.509</v>
+        <v>-2.8501</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8421999999999999</v>
+        <v>0.1045</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3512</v>
+        <v>-2.9546</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5417999999999999</v>
+        <v>-1.8581</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4501</v>
+        <v>0.2067</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9919</v>
+        <v>-2.0647</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0328</v>
+        <v>-0.9921</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3921</v>
+        <v>-0.1022</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3592</v>
+        <v>-0.8899</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2893</v>
+        <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9969</v>
+        <v>0.0791</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8110000000000001</v>
+        <v>0.0386</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1859</v>
+        <v>0.0405</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.9848</v>
+        <v>-1.2843</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.5686</v>
+        <v>-1.2843</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.2448</v>
+        <v>-4.2804</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.569</v>
+        <v>-1.0333</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6757</v>
+        <v>-3.2471</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3411</v>
@@ -2014,13 +2014,13 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.963</v>
+        <v>0.0014</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4567</v>
+        <v>0.0791</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5063</v>
+        <v>-0.0776</v>
       </c>
       <c r="V20" t="n">
         <v>-2.565</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>J. BERGENS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.9088</v>
+        <v>-5.2083</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.3742</v>
+        <v>-7.1645</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5345</v>
+        <v>1.9562</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.1817</v>
+        <v>-6.0792</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.9026</v>
+        <v>-4.1753</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7209</v>
+        <v>-1.9039</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.3201</v>
+        <v>-4.6747</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.3593</v>
+        <v>-3.1585</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0392</v>
+        <v>-1.5161</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8616</v>
+        <v>-1.4045</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5434</v>
+        <v>-1.0167</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6817</v>
+        <v>-0.3878</v>
       </c>
       <c r="P21" t="n">
         <v>-1.4568</v>
@@ -2092,28 +2092,28 @@
         <v>2.7055</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9481</v>
+        <v>0.0138</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9407</v>
+        <v>-0.8748</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0074</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2183</v>
+        <v>2.3138</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>2.5473</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.3858</v>
+        <v>-0.2335</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. BERGENS</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0044</v>
+        <v>-6.9065</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.7003</v>
+        <v>-6.3386</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6958</v>
+        <v>-0.5678</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.0792</v>
+        <v>-4.1817</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.1753</v>
+        <v>-4.9026</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9039</v>
+        <v>0.7209</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.6747</v>
+        <v>-3.3201</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.1585</v>
+        <v>-3.3593</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5161</v>
+        <v>0.0392</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4045</v>
+        <v>-0.8616</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0167</v>
+        <v>-1.5434</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3878</v>
+        <v>0.6817</v>
       </c>
       <c r="P22" t="n">
         <v>-1.4568</v>
@@ -2170,22 +2170,22 @@
         <v>2.7055</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7823</v>
+        <v>0.9504</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4106</v>
+        <v>-0.0237</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6283</v>
+        <v>0.9741</v>
       </c>
       <c r="V22" t="n">
-        <v>2.3138</v>
+        <v>-2.2183</v>
       </c>
       <c r="W22" t="n">
-        <v>2.5473</v>
+        <v>1.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2335</v>
+        <v>-3.3858</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-27.2315</v>
+        <v>-25.0885</v>
       </c>
       <c r="E23" t="n">
         <v>-24.6576</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5739</v>
+        <v>-0.4306000000000009</v>
       </c>
       <c r="G23" t="n">
         <v>-20.289</v>
@@ -2218,7 +2218,7 @@
         <v>-17.4315</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8573</v>
+        <v>-2.857300000000001</v>
       </c>
       <c r="J23" t="n">
         <v>-11.0206</v>
@@ -2248,13 +2248,13 @@
         <v>19.7711</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.01670000000000016</v>
+        <v>2.1265</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.4976</v>
+        <v>-3.4974</v>
       </c>
       <c r="U23" t="n">
-        <v>3.4809</v>
+        <v>5.6243</v>
       </c>
       <c r="V23" t="n">
         <v>-10.0478</v>
